--- a/КПП/Том СОТ КПП/Журнал входного контроля СОТ КПП.xlsx
+++ b/КПП/Том СОТ КПП/Журнал входного контроля СОТ КПП.xlsx
@@ -508,7 +508,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:K38"/>
+  <dimension ref="A1:K37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1515,102 +1515,49 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="10" t="n">
-        <v>16</v>
-      </c>
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>16.10.2026</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>Автоматизированное рабочее место (два монитора) (поз. АРК2)</t>
-        </is>
-      </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="10" t="inlineStr">
-        <is>
-          <t>шт.</t>
-        </is>
-      </c>
-      <c r="F32" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="G32" s="11" t="inlineStr">
-        <is>
-          <t>Паспорт (руководство по эксплуатации) изготовителя</t>
-        </is>
-      </c>
-      <c r="H32" s="11" t="inlineStr">
-        <is>
-          <t>Внешний осмотр, маркировка, комплектность — без замечаний. Паспорт изготовителя в наличии (оригинал).</t>
-        </is>
-      </c>
-      <c r="I32" s="11" t="inlineStr">
-        <is>
-          <t>Соответствует. Допущено к применению</t>
-        </is>
-      </c>
-      <c r="J32" s="11" t="inlineStr">
-        <is>
-          <t>Иванчук М.В.</t>
-        </is>
-      </c>
-      <c r="K32" s="11" t="inlineStr">
-        <is>
-          <t>ИД лист 2</t>
+    <row r="33">
+      <c r="A33" s="12" t="inlineStr">
+        <is>
+          <t>Ответственный за входной контроль (лицо, выполняющее работы)</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
-        <is>
-          <t>Ответственный за входной контроль (лицо, выполняющее работы)</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="13" t="inlineStr">
+      <c r="A34" s="13" t="inlineStr">
         <is>
           <t>начальник отдела систем технической безопасности ООО «АльтЭн» Иванчук М.В.</t>
         </is>
       </c>
-      <c r="G35" s="14" t="inlineStr">
+      <c r="G34" s="14" t="inlineStr">
         <is>
           <t>____________________ (подпись)</t>
         </is>
       </c>
-      <c r="I35" s="14" t="inlineStr">
+      <c r="I34" s="14" t="inlineStr">
         <is>
           <t>«____» ____________ 2026 г.</t>
         </is>
       </c>
     </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>Представитель лица, осуществляющего строительство</t>
+        </is>
+      </c>
+    </row>
     <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>Представитель лица, осуществляющего строительство</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="13" t="inlineStr">
+      <c r="A37" s="13" t="inlineStr">
         <is>
           <t>руководитель проекта Белоногов И.Ю.</t>
         </is>
       </c>
-      <c r="G38" s="14" t="inlineStr">
+      <c r="G37" s="14" t="inlineStr">
         <is>
           <t>____________________ (подпись)</t>
         </is>
       </c>
-      <c r="I38" s="14" t="inlineStr">
+      <c r="I37" s="14" t="inlineStr">
         <is>
           <t>«____» ____________ 2026 г.</t>
         </is>
@@ -1618,24 +1565,24 @@
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="A34:K34"/>
     <mergeCell ref="A15:K15"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="I37:K37"/>
     <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A36:K36"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A6:K6"/>
-    <mergeCell ref="G38:H38"/>
     <mergeCell ref="A7:K7"/>
-    <mergeCell ref="A35:F35"/>
-    <mergeCell ref="I35:K35"/>
-    <mergeCell ref="A37:K37"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="G37:H37"/>
+    <mergeCell ref="G34:H34"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="I34:K34"/>
     <mergeCell ref="A5:K5"/>
     <mergeCell ref="A23:K23"/>
     <mergeCell ref="A8:K8"/>
-    <mergeCell ref="G35:H35"/>
     <mergeCell ref="A10:K10"/>
     <mergeCell ref="A9:K9"/>
   </mergeCells>
